--- a/工程设计.xlsx
+++ b/工程设计.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="20752" windowHeight="9555" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="硬件缺失" sheetId="5" r:id="rId5"/>
     <sheet name="时钟与频率" sheetId="6" r:id="rId6"/>
     <sheet name="流程" sheetId="7" r:id="rId7"/>
+    <sheet name="需求分析" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="81">
   <si>
     <t>1.Foc</t>
   </si>
@@ -257,6 +258,30 @@
   </si>
   <si>
     <t>8.更新 pwm</t>
+  </si>
+  <si>
+    <t>驱动控制板 主控板</t>
+  </si>
+  <si>
+    <t>采集射击但量、电机温度</t>
+  </si>
+  <si>
+    <t>软启动功能</t>
+  </si>
+  <si>
+    <t>拉拽启动</t>
+  </si>
+  <si>
+    <t>低温启动加热、保温（？）、高温限制功率、超温停机</t>
+  </si>
+  <si>
+    <t>指令功能、故障信息、协议</t>
+  </si>
+  <si>
+    <t>依靠感知负载电流变化，感知枪械拖拽力，实现被动触发和自适应供弹</t>
+  </si>
+  <si>
+    <t>电流、速度滤波</t>
   </si>
 </sst>
 </file>
@@ -269,10 +294,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -756,144 +788,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1217,7 +1252,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="4">
+      <c r="A1" s="5">
         <v>46260</v>
       </c>
       <c r="B1" t="s">
@@ -1256,13 +1291,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D1" t="s">
@@ -1270,10 +1305,10 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
@@ -1284,96 +1319,96 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
       <c r="D3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="D4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1618,7 +1653,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1"/>
+    <row r="13" s="2" customFormat="1"/>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>56</v>
@@ -1628,7 +1663,6 @@
       <c r="A17" t="s">
         <v>57</v>
       </c>
-      <c r="B17"/>
       <c r="F17" t="s">
         <v>58</v>
       </c>
@@ -1689,6 +1723,58 @@
     <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/工程设计.xlsx
+++ b/工程设计.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
   <si>
     <t>1.Foc</t>
   </si>
@@ -282,6 +282,15 @@
   </si>
   <si>
     <t>电流、速度滤波</t>
+  </si>
+  <si>
+    <t>李修：启动时速度调高，后续降低</t>
+  </si>
+  <si>
+    <t>无刷永磁同步 转速越高，扭矩越大</t>
+  </si>
+  <si>
+    <t>通信部分：</t>
   </si>
 </sst>
 </file>
@@ -1734,8 +1743,8 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -1775,6 +1784,21 @@
     <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/工程设计.xlsx
+++ b/工程设计.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="88">
   <si>
     <t>1.Foc</t>
   </si>
@@ -291,6 +291,18 @@
   </si>
   <si>
     <t>通信部分：</t>
+  </si>
+  <si>
+    <t>预处理：校准方向，校准极对数，调整pi参数</t>
+  </si>
+  <si>
+    <t>待机：温控、状态监测、采集电流、CAN上报待机</t>
+  </si>
+  <si>
+    <t>运行：</t>
+  </si>
+  <si>
+    <t>自检</t>
   </si>
 </sst>
 </file>
@@ -1743,7 +1755,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1801,6 +1813,26 @@
         <v>83</v>
       </c>
     </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/工程设计.xlsx
+++ b/工程设计.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555" firstSheet="1" activeTab="7"/>
+    <workbookView windowWidth="20752" windowHeight="9555" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="时钟与频率" sheetId="6" r:id="rId6"/>
     <sheet name="流程" sheetId="7" r:id="rId7"/>
     <sheet name="需求分析" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet3" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
   <si>
     <t>1.Foc</t>
   </si>
@@ -303,6 +304,30 @@
   </si>
   <si>
     <t>自检</t>
+  </si>
+  <si>
+    <t>复合功能</t>
+  </si>
+  <si>
+    <t>foc</t>
+  </si>
+  <si>
+    <t>1.timer触发adc</t>
+  </si>
+  <si>
+    <t>2.adc采样后进入中断服务函数</t>
+  </si>
+  <si>
+    <t>3.获取ia,ic</t>
+  </si>
+  <si>
+    <t>4.spi获取ma,ea</t>
+  </si>
+  <si>
+    <t>5.pi获取输出v_dq</t>
+  </si>
+  <si>
+    <t>6.svpwm获取输出d_abc并更新</t>
   </si>
 </sst>
 </file>
@@ -1837,4 +1862,54 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/工程设计.xlsx
+++ b/工程设计.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555" firstSheet="1" activeTab="8"/>
+    <workbookView windowWidth="20752" windowHeight="9555" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
   <si>
     <t>1.Foc</t>
   </si>
@@ -304,6 +304,36 @@
   </si>
   <si>
     <t>自检</t>
+  </si>
+  <si>
+    <t>缺少的硬件：</t>
+  </si>
+  <si>
+    <t>温度传感器</t>
+  </si>
+  <si>
+    <t>加热片</t>
+  </si>
+  <si>
+    <t>接近开关</t>
+  </si>
+  <si>
+    <t>上位机</t>
+  </si>
+  <si>
+    <t>缺少的功能：</t>
+  </si>
+  <si>
+    <t>温控</t>
+  </si>
+  <si>
+    <t>状态监测</t>
+  </si>
+  <si>
+    <t>故障监测</t>
+  </si>
+  <si>
+    <t>can通信</t>
   </si>
   <si>
     <t>复合功能</t>
@@ -1780,8 +1810,8 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -1856,6 +1886,61 @@
     <row r="29" spans="1:1">
       <c r="A29" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="B45" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="B46" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1872,40 +1957,40 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
